--- a/data/ciudad_de_dios.xlsx
+++ b/data/ciudad_de_dios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,25 +457,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -500,18 +515,27 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -534,18 +558,27 @@
         <v>11</v>
       </c>
       <c r="F3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="n">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -568,18 +601,27 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>17</v>
       </c>
-      <c r="H4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -602,18 +644,27 @@
         <v>11</v>
       </c>
       <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
         <v>7</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>17</v>
       </c>
-      <c r="H5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
         <v>16</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -636,18 +687,27 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I6" t="n">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>18</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -670,18 +730,27 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>7</v>
       </c>
       <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -704,18 +773,27 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -738,18 +816,27 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" t="n">
         <v>22</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>13</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>22</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -772,18 +859,27 @@
         <v>13</v>
       </c>
       <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="n">
         <v>7</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>17</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>16</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>12</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -806,18 +902,27 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
+        <v>17</v>
+      </c>
+      <c r="G11" t="n">
         <v>14</v>
       </c>
-      <c r="G11" t="n">
-        <v>15</v>
-      </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" t="n">
         <v>20</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -840,18 +945,27 @@
         <v>15</v>
       </c>
       <c r="F12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
         <v>6</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>16</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>16</v>
       </c>
-      <c r="I12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M12" t="n">
         <v>14</v>
       </c>
     </row>
@@ -866,7 +980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,25 +1011,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -931,15 +1060,18 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -969,25 +1101,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1021,25 +1168,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1073,25 +1235,40 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1125,25 +1302,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1171,27 +1363,30 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1203,15 +1398,18 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1241,25 +1439,36 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1293,25 +1502,40 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1345,25 +1569,40 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1397,25 +1636,40 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>14</t>
         </is>

--- a/data/ciudad_de_dios.xlsx
+++ b/data/ciudad_de_dios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,25 +472,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -524,18 +534,24 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -567,18 +583,24 @@
         <v>9</v>
       </c>
       <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
         <v>9</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>17</v>
       </c>
-      <c r="K3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L3" t="n">
-        <v>15</v>
-      </c>
       <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -610,18 +632,24 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="n">
         <v>9</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
         <v>17</v>
       </c>
-      <c r="K4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15</v>
-      </c>
       <c r="M4" t="n">
+        <v>15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -653,18 +681,24 @@
         <v>8</v>
       </c>
       <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>17</v>
       </c>
-      <c r="K5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" t="n">
         <v>16</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -696,18 +730,24 @@
         <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
         <v>14</v>
       </c>
       <c r="L6" t="n">
+        <v>18</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
         <v>20</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -739,18 +779,24 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="n">
         <v>7</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>17</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>7</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -782,18 +828,24 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -828,15 +880,21 @@
         <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
         <v>22</v>
       </c>
       <c r="M9" t="n">
+        <v>13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>22</v>
+      </c>
+      <c r="O9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -868,18 +926,24 @@
         <v>12</v>
       </c>
       <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>17</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>16</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>12</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -914,15 +978,21 @@
         <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15</v>
+      </c>
+      <c r="N11" t="n">
         <v>20</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -954,18 +1024,24 @@
         <v>11</v>
       </c>
       <c r="I12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>16</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>16</v>
       </c>
-      <c r="L12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" t="n">
         <v>14</v>
       </c>
     </row>
@@ -980,7 +1056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,25 +1102,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1063,15 +1149,17 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1116,25 +1204,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1183,25 +1281,35 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1250,25 +1358,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1317,25 +1435,35 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1368,25 +1496,35 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1401,15 +1539,17 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1455,20 +1595,30 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1517,25 +1667,35 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1589,20 +1749,30 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1651,25 +1821,35 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>14</t>
         </is>

--- a/data/ciudad_de_dios.xlsx
+++ b/data/ciudad_de_dios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,25 +482,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -540,11 +545,11 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -552,6 +557,9 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -589,18 +597,21 @@
         <v>10</v>
       </c>
       <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
         <v>9</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>17</v>
       </c>
-      <c r="M3" t="n">
-        <v>15</v>
-      </c>
       <c r="N3" t="n">
         <v>15</v>
       </c>
       <c r="O3" t="n">
+        <v>15</v>
+      </c>
+      <c r="P3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -638,18 +649,21 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
         <v>9</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>17</v>
       </c>
-      <c r="M4" t="n">
-        <v>15</v>
-      </c>
       <c r="N4" t="n">
         <v>15</v>
       </c>
       <c r="O4" t="n">
+        <v>15</v>
+      </c>
+      <c r="P4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -687,18 +701,21 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
         <v>7</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>17</v>
       </c>
-      <c r="M5" t="n">
-        <v>15</v>
-      </c>
       <c r="N5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O5" t="n">
         <v>16</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -736,18 +753,21 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
         <v>14</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>18</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>14</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>20</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -785,18 +805,21 @@
         <v>13</v>
       </c>
       <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="n">
         <v>7</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>12</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>17</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>7</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -834,11 +857,11 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -846,6 +869,9 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -883,18 +909,21 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M9" t="n">
         <v>22</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>13</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>22</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -932,18 +961,21 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
         <v>7</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>17</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>16</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>12</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -981,18 +1013,21 @@
         <v>9</v>
       </c>
       <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
         <v>14</v>
       </c>
-      <c r="L11" t="n">
-        <v>15</v>
-      </c>
       <c r="M11" t="n">
         <v>15</v>
       </c>
       <c r="N11" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" t="n">
         <v>20</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1030,18 +1065,21 @@
         <v>10</v>
       </c>
       <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="n">
         <v>6</v>
-      </c>
-      <c r="L12" t="n">
-        <v>16</v>
       </c>
       <c r="M12" t="n">
         <v>16</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
+        <v>15</v>
+      </c>
+      <c r="P12" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1056,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,25 +1150,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1151,15 +1194,16 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1214,25 +1258,30 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1291,25 +1340,30 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1368,25 +1422,30 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1445,25 +1504,30 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1506,25 +1570,30 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1541,15 +1610,16 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1600,25 +1670,30 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1677,25 +1752,30 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1754,14 +1834,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>15</t>
@@ -1769,10 +1849,15 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1831,25 +1916,30 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="O12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>14</t>
         </is>

--- a/data/ciudad_de_dios.xlsx
+++ b/data/ciudad_de_dios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,25 +487,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -548,11 +553,11 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -560,6 +565,9 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -600,18 +608,21 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
         <v>9</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>17</v>
       </c>
-      <c r="N3" t="n">
-        <v>15</v>
-      </c>
       <c r="O3" t="n">
         <v>15</v>
       </c>
       <c r="P3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -652,18 +663,21 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="n">
         <v>9</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>17</v>
       </c>
-      <c r="N4" t="n">
-        <v>15</v>
-      </c>
       <c r="O4" t="n">
         <v>15</v>
       </c>
       <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -704,18 +718,21 @@
         <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="n">
         <v>7</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>17</v>
       </c>
-      <c r="N5" t="n">
-        <v>15</v>
-      </c>
       <c r="O5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P5" t="n">
         <v>16</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -756,18 +773,21 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
         <v>14</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>18</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>14</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>20</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -808,18 +828,21 @@
         <v>9</v>
       </c>
       <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>12</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>17</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>7</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -860,11 +883,11 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -872,6 +895,9 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -912,18 +938,21 @@
         <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
+        <v>15</v>
+      </c>
+      <c r="N9" t="n">
         <v>22</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>13</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>22</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -964,18 +993,21 @@
         <v>10</v>
       </c>
       <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
         <v>7</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>17</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>16</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>12</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1016,18 +1048,21 @@
         <v>10</v>
       </c>
       <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" t="n">
         <v>14</v>
       </c>
-      <c r="M11" t="n">
-        <v>15</v>
-      </c>
       <c r="N11" t="n">
         <v>15</v>
       </c>
       <c r="O11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" t="n">
         <v>20</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1068,18 +1103,21 @@
         <v>9</v>
       </c>
       <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
         <v>6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>16</v>
       </c>
       <c r="N12" t="n">
         <v>16</v>
       </c>
       <c r="O12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1094,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,25 +1193,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1195,15 +1238,16 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1263,25 +1307,30 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1345,25 +1394,30 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1427,25 +1481,30 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1509,25 +1568,30 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1575,25 +1639,30 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1611,15 +1680,16 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1675,25 +1745,30 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1757,25 +1832,30 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1839,14 +1919,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>15</t>
@@ -1854,10 +1934,15 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1921,25 +2006,30 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>14</t>
         </is>

--- a/data/ciudad_de_dios.xlsx
+++ b/data/ciudad_de_dios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -556,18 +571,27 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -611,18 +635,27 @@
         <v>11</v>
       </c>
       <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P3" t="n">
         <v>9</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>17</v>
       </c>
-      <c r="O3" t="n">
-        <v>15</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
+        <v>15</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -666,18 +699,27 @@
         <v>11</v>
       </c>
       <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
         <v>9</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>17</v>
       </c>
-      <c r="O4" t="n">
-        <v>15</v>
-      </c>
-      <c r="P4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
+        <v>15</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -721,18 +763,27 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
         <v>7</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q5" t="n">
         <v>17</v>
       </c>
-      <c r="O5" t="n">
-        <v>15</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
+        <v>15</v>
+      </c>
+      <c r="S5" t="n">
         <v>16</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -776,18 +827,27 @@
         <v>4</v>
       </c>
       <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>9</v>
+      </c>
+      <c r="P6" t="n">
         <v>14</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>18</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>14</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>20</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -831,18 +891,27 @@
         <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P7" t="n">
         <v>7</v>
       </c>
       <c r="Q7" t="n">
+        <v>12</v>
+      </c>
+      <c r="R7" t="n">
+        <v>17</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -886,18 +955,27 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>6</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -941,18 +1019,27 @@
         <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
+        <v>9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="n">
         <v>22</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>13</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>22</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -996,18 +1083,27 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
         <v>7</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" t="n">
         <v>17</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>16</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1051,18 +1147,27 @@
         <v>4</v>
       </c>
       <c r="M11" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
         <v>14</v>
       </c>
-      <c r="N11" t="n">
-        <v>15</v>
-      </c>
-      <c r="O11" t="n">
-        <v>15</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
+        <v>15</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15</v>
+      </c>
+      <c r="S11" t="n">
         <v>20</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1106,18 +1211,27 @@
         <v>2</v>
       </c>
       <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>16</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>16</v>
       </c>
-      <c r="P12" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1132,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,25 +1312,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1239,15 +1368,18 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1312,25 +1444,36 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1399,25 +1542,40 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1486,25 +1644,40 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1573,25 +1746,40 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1644,25 +1832,40 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1681,15 +1884,18 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1750,25 +1956,40 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1837,25 +2058,40 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1924,25 +2160,40 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2011,25 +2262,40 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>14</t>
         </is>

--- a/data/ciudad_de_dios.xlsx
+++ b/data/ciudad_de_dios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,25 +507,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -580,11 +585,11 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -592,6 +597,9 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -644,18 +652,21 @@
         <v>12</v>
       </c>
       <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>9</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>17</v>
       </c>
-      <c r="R3" t="n">
-        <v>15</v>
-      </c>
       <c r="S3" t="n">
         <v>15</v>
       </c>
       <c r="T3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U3" t="n">
         <v>10</v>
       </c>
     </row>
@@ -708,18 +719,21 @@
         <v>8</v>
       </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>17</v>
       </c>
-      <c r="R4" t="n">
-        <v>15</v>
-      </c>
       <c r="S4" t="n">
         <v>15</v>
       </c>
       <c r="T4" t="n">
+        <v>15</v>
+      </c>
+      <c r="U4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -772,18 +786,21 @@
         <v>7</v>
       </c>
       <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>7</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>17</v>
       </c>
-      <c r="R5" t="n">
-        <v>15</v>
-      </c>
       <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="n">
         <v>16</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -836,18 +853,21 @@
         <v>9</v>
       </c>
       <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>18</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>14</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>20</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -900,18 +920,21 @@
         <v>14</v>
       </c>
       <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>12</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>17</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>7</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -964,11 +987,11 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -976,6 +999,9 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1028,18 +1054,21 @@
         <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="n">
         <v>22</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>13</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>22</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1092,18 +1121,21 @@
         <v>7</v>
       </c>
       <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>17</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>16</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>12</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1156,18 +1188,21 @@
         <v>10</v>
       </c>
       <c r="P11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" t="n">
         <v>14</v>
       </c>
-      <c r="Q11" t="n">
-        <v>15</v>
-      </c>
       <c r="R11" t="n">
         <v>15</v>
       </c>
       <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="n">
         <v>20</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1220,18 +1255,21 @@
         <v>7</v>
       </c>
       <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>16</v>
       </c>
       <c r="R12" t="n">
         <v>16</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T12" t="n">
+        <v>15</v>
+      </c>
+      <c r="U12" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1246,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1327,25 +1365,30 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1371,15 +1414,16 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1455,25 +1499,30 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1557,25 +1606,30 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1659,25 +1713,30 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1761,25 +1820,30 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1847,25 +1911,30 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1887,15 +1956,16 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1971,25 +2041,30 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2073,25 +2148,30 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2175,14 +2255,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>15</t>
@@ -2190,10 +2270,15 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2277,25 +2362,30 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
